--- a/Docs/TablasDatos-Lab6.xlsx
+++ b/Docs/TablasDatos-Lab6.xlsx
@@ -169,7 +169,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -204,6 +204,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3252,29 +3253,45 @@
       <c r="A3" s="8">
         <v>0.1</v>
       </c>
-      <c r="B3" s="5"/>
-      <c r="C3" s="7"/>
+      <c r="B3" s="5">
+        <v>467473.71</v>
+      </c>
+      <c r="C3" s="7">
+        <v>5220.95</v>
+      </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="9">
         <v>0.5</v>
       </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="7"/>
+      <c r="B4" s="2">
+        <v>379216.05</v>
+      </c>
+      <c r="C4" s="7">
+        <v>4574.15</v>
+      </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="8">
         <v>0.7</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="7"/>
+      <c r="B5" s="2">
+        <v>372786.26</v>
+      </c>
+      <c r="C5" s="7">
+        <v>4553.14</v>
+      </c>
     </row>
     <row r="6" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="10">
         <v>0.9</v>
       </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="7"/>
+      <c r="B6" s="2">
+        <v>368142.48</v>
+      </c>
+      <c r="C6" s="7">
+        <v>4987.85</v>
+      </c>
     </row>
     <row r="9" spans="1:3" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
@@ -3298,29 +3315,45 @@
       <c r="A11" s="2">
         <v>2</v>
       </c>
-      <c r="B11" s="2"/>
-      <c r="C11" s="5"/>
+      <c r="B11" s="2">
+        <v>397909.79</v>
+      </c>
+      <c r="C11" s="5">
+        <v>4110.82</v>
+      </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>4</v>
       </c>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
+      <c r="B12" s="2">
+        <v>393473.35</v>
+      </c>
+      <c r="C12" s="2">
+        <v>4221.24</v>
+      </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>6</v>
       </c>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
+      <c r="B13" s="2">
+        <v>392405.39</v>
+      </c>
+      <c r="C13" s="2">
+        <v>4306.62</v>
+      </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>8</v>
       </c>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
+      <c r="B14" s="2">
+        <v>392380.81</v>
+      </c>
+      <c r="C14" s="2">
+        <v>4398.8</v>
+      </c>
     </row>
     <row r="23" ht="14.65" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
